--- a/data/中幼林抚育-网格填表模板.xlsx
+++ b/data/中幼林抚育-网格填表模板.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1435" uniqueCount="1435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="1436">
   <si>
     <t/>
   </si>
@@ -4319,6 +4319,9 @@
   </si>
   <si>
     <t>项目名称|select;小班号|search</t>
+  </si>
+  <si>
+    <t>搜索控件配置；项间用 ; 分隔，项内为 字段|控件类型；select=下拉（适合选项少的字段）；search=前端本地搜索选中（输入即时过滤已加载的行，不发服务端请求，适合选项过多的字段，如小班号）；字段名必须与数据sheet表头一致</t>
   </si>
 </sst>
 </file>
@@ -39631,7 +39634,7 @@
         <v>1418</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>1428</v>
+        <v>1435</v>
       </c>
       <c r="F9" t="s">
         <v>1434</v>

--- a/data/中幼林抚育-网格填表模板.xlsx
+++ b/data/中幼林抚育-网格填表模板.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="1436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1428" uniqueCount="1428">
   <si>
     <t/>
   </si>
@@ -4177,25 +4177,79 @@
     <t>哈喽村委会</t>
   </si>
   <si>
+    <t>key</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>类型</t>
+  </si>
+  <si>
+    <t>默认值</t>
+  </si>
+  <si>
+    <t>说明</t>
+  </si>
+  <si>
+    <t>示例</t>
+  </si>
+  <si>
     <t>相片备注</t>
   </si>
   <si>
-    <t>{{项目名称}}{{标段}}小班{{小班号}}{{sheet名称}}</t>
+    <t>{{项目名称}}{{标段}}小班{{小班号}}</t>
+  </si>
+  <si>
+    <t>模板</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>拍照水印备注模板；{{列名}}占位符替换为数据行对应列的值，{{sheet名称}}替换为当前sheet名</t>
+  </si>
+  <si>
+    <t>XX项目一标段小班12</t>
+  </si>
+  <si>
+    <t>相片文件名</t>
+  </si>
+  <si>
+    <t>{{分类}}_{{乡镇}}_{{村}}_{{小班号}}_{{时间}}</t>
+  </si>
+  <si>
+    <t>同value</t>
+  </si>
+  <si>
+    <t>照片文件名模板（不含扩展名）；段间用半角下划线 _ 连接；{{时间}}=YYYYMMDD_HHMMSS</t>
+  </si>
+  <si>
+    <t>抚育_甲乡_乙村_12_20260911_153000</t>
   </si>
   <si>
     <t>目录</t>
   </si>
   <si>
-    <t>sheet名称/小班号{{小班号}}</t>
-  </si>
-  <si>
-    <t>主要目录分隔符和占位符</t>
+    <t>{{sheet名称}}/{{小班号}}</t>
+  </si>
+  <si>
+    <t>照片保存子目录模板；半角斜杠 / 为目录分隔符；段内可混排普通文本与占位符，如 {{小班号}}号调查小班</t>
+  </si>
+  <si>
+    <t>中幼林抚育验收/小班号12</t>
   </si>
   <si>
     <t>验收结果选项</t>
   </si>
   <si>
-    <t>合格|不合格</t>
+    <t>合格;不合格</t>
+  </si>
+  <si>
+    <t>列表</t>
+  </si>
+  <si>
+    <t>「验收结果」列的下拉选项；多值用半角分号 ; 分隔</t>
   </si>
   <si>
     <t>可编辑列</t>
@@ -4204,124 +4258,46 @@
     <t>验收人;验收日期;验收结果;验收备注</t>
   </si>
   <si>
+    <t>允许用户编辑的列名清单；多值用 ; 分隔；列名必须与数据sheet表头完全一致</t>
+  </si>
+  <si>
+    <t>验收人;验收日期</t>
+  </si>
+  <si>
     <t>不显示列</t>
   </si>
   <si>
-    <t>没有不显示列则都显示</t>
+    <t>（空）</t>
+  </si>
+  <si>
+    <t>需要隐藏的列名清单；留空=全部显示；多值用 ; 分隔</t>
   </si>
   <si>
     <t>功能</t>
   </si>
   <si>
-    <t>拍照｜轨迹</t>
+    <t>拍照;轨迹</t>
+  </si>
+  <si>
+    <t>启用的功能开关；可选值：拍照、轨迹、打卡；多值用 ; 分隔</t>
   </si>
   <si>
     <t>搜索选项</t>
   </si>
   <si>
-    <t>项目名称|select;标段|select;小班号|search;小班号;select</t>
-  </si>
-  <si>
-    <t>html元素备注，联动</t>
-  </si>
-  <si>
-    <t>key</t>
-  </si>
-  <si>
-    <t>相片文件名</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>{{项目名称}}{{标段}}小班{{小班号}}</t>
-  </si>
-  <si>
-    <t>{{分类}}_{{乡镇}}_{{村}}_{{小班号}}_{{时间}}</t>
-  </si>
-  <si>
-    <t>{{sheet名称}}/{{小班号}}</t>
-  </si>
-  <si>
-    <t>合格;不合格</t>
-  </si>
-  <si>
-    <t>拍照;轨迹</t>
-  </si>
-  <si>
     <t>项目名称|select;标段|select;小班号|search</t>
   </si>
   <si>
-    <t>类型</t>
-  </si>
-  <si>
-    <t>模板</t>
-  </si>
-  <si>
-    <t>列表</t>
-  </si>
-  <si>
     <t>控件映射</t>
   </si>
   <si>
-    <t>默认值</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>同value</t>
-  </si>
-  <si>
-    <t>（空）</t>
-  </si>
-  <si>
-    <t>说明</t>
-  </si>
-  <si>
-    <t>拍照水印备注模板；{{列名}}占位符替换为数据行对应列的值，{{sheet名称}}替换为当前sheet名</t>
-  </si>
-  <si>
-    <t>照片文件名模板（不含扩展名）；段间用半角下划线 _ 连接；{{时间}}=YYYYMMDD_HHMMSS</t>
-  </si>
-  <si>
-    <t>照片保存子目录模板；半角斜杠 / 为目录分隔符；段内可混排普通文本与占位符，如 {{小班号}}号调查小班</t>
-  </si>
-  <si>
-    <t>「验收结果」列的下拉选项；多值用半角分号 ; 分隔</t>
-  </si>
-  <si>
-    <t>允许用户编辑的列名清单；多值用 ; 分隔；列名必须与数据sheet表头完全一致</t>
-  </si>
-  <si>
-    <t>需要隐藏的列名清单；留空=全部显示；多值用 ; 分隔</t>
-  </si>
-  <si>
-    <t>启用的功能开关；可选值：拍照、轨迹、打卡；多值用 ; 分隔</t>
-  </si>
-  <si>
     <t>搜索控件配置；项间用 ; 分隔，项内为 字段|控件类型（select=下拉、search=文本搜索）；字段名必须与数据sheet表头一致；此项修正原值中的笔误「小班号;select」并去除多余的反斜杠</t>
   </si>
   <si>
-    <t>示例</t>
-  </si>
-  <si>
-    <t>XX项目一标段小班12</t>
-  </si>
-  <si>
-    <t>抚育_甲乡_乙村_12_20260911_153000</t>
-  </si>
-  <si>
-    <t>中幼林抚育验收/小班号12</t>
-  </si>
-  <si>
-    <t>验收人;验收日期</t>
-  </si>
-  <si>
     <t>项目名称|select;小班号|search</t>
   </si>
   <si>
-    <t>搜索控件配置；项间用 ; 分隔，项内为 字段|控件类型；select=下拉（适合选项少的字段）；search=前端本地搜索选中（输入即时过滤已加载的行，不发服务端请求，适合选项过多的字段，如小班号）；字段名必须与数据sheet表头一致</t>
+    <t>{{标段}}_{{乡镇}}_{{村}}_{{小班号}}_{{时间}}</t>
   </si>
 </sst>
 </file>
@@ -4330,10 +4306,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="6">
     <numFmt numFmtId="300" formatCode="General"/>
-    <numFmt numFmtId="301" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="301" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="302" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="303" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="304" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="303" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="304" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="305" formatCode="0%"/>
   </numFmts>
   <fonts count="28">
@@ -4375,14 +4351,6 @@
       <name val="宋体"/>
       <charset val="134"/>
       <b val="1"/>
-      <color theme="1"/>
-      <sz val="12"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
       <i val="0"/>
       <color theme="1"/>
       <sz val="12"/>
@@ -4395,14 +4363,15 @@
     <font>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="0"/>
+      <charset val="134"/>
+      <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
@@ -4416,52 +4385,22 @@
     <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF9C6500"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF006100"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
@@ -4470,7 +4409,39 @@
       <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4486,52 +4457,13 @@
       <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
@@ -4539,7 +4471,51 @@
       <name val="宋体"/>
       <charset val="0"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
@@ -4562,7 +4538,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399976"/>
+        <fgColor theme="8" tint="0.599994"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799982"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799982"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599994"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399976"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799982"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599994"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399976"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799982"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599994"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399976"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799982"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599994"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799982"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399976"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4574,115 +4700,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399976"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799982"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399976"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599994"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799982"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399976"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599994"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799982"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399976"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599994"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799982"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399976"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599994"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799982"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4694,55 +4712,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9" tint="0.399976"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799982"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599994"/>
+        <fgColor theme="7" tint="0.399976"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4778,12 +4754,40 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -4792,8 +4796,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499985"/>
       </bottom>
       <diagonal/>
     </border>
@@ -4831,47 +4835,19 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499985"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -4883,28 +4859,73 @@
     <xf numFmtId="300" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="300" fontId="10" fillId="5" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="300" fontId="10" fillId="5" borderId="3" xfId="0" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="11" fillId="3" borderId="2" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="301" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="300" fontId="9" fillId="6" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="300" fontId="9" fillId="7" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="300" fontId="12" fillId="7" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="300" fontId="10" fillId="8" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="300" fontId="13" fillId="3" borderId="2" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="300" fontId="9" fillId="9" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="302" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="300" fontId="9" fillId="10" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="300" fontId="14" fillId="3" borderId="2" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="300" fontId="10" fillId="11" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="303" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="300" fontId="10" fillId="12" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="300" fontId="15" fillId="3" borderId="2" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="16" fillId="3" borderId="2" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="8" fillId="8" borderId="4" xfId="0" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="17" fillId="3" borderId="5" xfId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="18" fillId="3" borderId="5" xfId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="19" fillId="3" borderId="6" xfId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="19" fillId="3" borderId="2" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="20" fillId="9" borderId="7" xfId="0" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="21" fillId="10" borderId="8" xfId="0" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="22" fillId="10" borderId="7" xfId="0" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="23" fillId="3" borderId="9" xfId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="24" fillId="3" borderId="10" xfId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="25" fillId="11" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="26" fillId="12" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="300" fontId="9" fillId="13" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4913,10 +4934,10 @@
     <xf numFmtId="300" fontId="9" fillId="14" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="300" fontId="10" fillId="15" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="300" fontId="27" fillId="15" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="300" fontId="10" fillId="16" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="300" fontId="27" fillId="16" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="300" fontId="9" fillId="17" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4925,10 +4946,10 @@
     <xf numFmtId="300" fontId="9" fillId="18" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="300" fontId="10" fillId="19" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="300" fontId="27" fillId="19" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="300" fontId="10" fillId="20" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="300" fontId="27" fillId="20" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="300" fontId="9" fillId="21" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4937,95 +4958,50 @@
     <xf numFmtId="300" fontId="9" fillId="22" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="300" fontId="10" fillId="23" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="300" fontId="27" fillId="23" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="300" fontId="10" fillId="24" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="300" fontId="9" fillId="24" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="300" fontId="9" fillId="25" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="300" fontId="11" fillId="26" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="300" fontId="27" fillId="26" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="300" fontId="12" fillId="27" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="300" fontId="9" fillId="27" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="300" fontId="13" fillId="3" borderId="3" xfId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="300" fontId="27" fillId="28" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="300" fontId="14" fillId="3" borderId="4" xfId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="300" fontId="15" fillId="28" borderId="5" xfId="0" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="300" fontId="16" fillId="28" borderId="6" xfId="0" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="300" fontId="17" fillId="29" borderId="5" xfId="0" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="300" fontId="18" fillId="3" borderId="2" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="300" fontId="18" fillId="3" borderId="7" xfId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="300" fontId="19" fillId="3" borderId="8" xfId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="300" fontId="20" fillId="3" borderId="8" xfId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="300" fontId="8" fillId="30" borderId="9" xfId="0" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="300" fontId="21" fillId="3" borderId="2" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="300" fontId="22" fillId="3" borderId="2" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="301" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="300" fontId="23" fillId="3" borderId="2" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="302" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="300" fontId="24" fillId="3" borderId="2" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="303" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="300" fontId="25" fillId="31" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="300" fontId="10" fillId="32" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="300" fontId="27" fillId="29" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="304" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="300" fontId="9" fillId="30" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="27" fillId="31" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="27" fillId="32" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="305" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="300" fontId="26" fillId="3" borderId="2" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="300" fontId="27" fillId="33" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="300" fontId="27" fillId="33" borderId="10" xfId="0" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="300" fontId="10" fillId="34" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="300" fontId="27" fillId="34" borderId="2" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5056,19 +5032,22 @@
     <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="300" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="300" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="300" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="7" fillId="2" borderId="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="300" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="300" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="300" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5077,54 +5056,54 @@
   </cellXfs>
   <cellStyles>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="1" builtinId="52"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="2" builtinId="51"/>
-    <cellStyle name="强调文字颜色 6" xfId="3" builtinId="49"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="4" builtinId="48"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="5" builtinId="46"/>
-    <cellStyle name="强调文字颜色 5" xfId="6" builtinId="45"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="7" builtinId="44"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="8" builtinId="43"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="9" builtinId="42"/>
-    <cellStyle name="强调文字颜色 4" xfId="10" builtinId="41"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="11" builtinId="40"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="12" builtinId="39"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="13" builtinId="38"/>
-    <cellStyle name="强调文字颜色 3" xfId="14" builtinId="37"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="15" builtinId="36"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="16" builtinId="35"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="17" builtinId="34"/>
-    <cellStyle name="强调文字颜色 2" xfId="18" builtinId="33"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="19" builtinId="32"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="20" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="21" builtinId="30"/>
-    <cellStyle name="强调文字颜色 1" xfId="22" builtinId="29"/>
-    <cellStyle name="适中" xfId="23" builtinId="28"/>
-    <cellStyle name="差" xfId="24" builtinId="27"/>
-    <cellStyle name="汇总" xfId="25" builtinId="25"/>
-    <cellStyle name="链接单元格" xfId="26" builtinId="24"/>
-    <cellStyle name="计算" xfId="27" builtinId="22"/>
-    <cellStyle name="输出" xfId="28" builtinId="21"/>
-    <cellStyle name="输入" xfId="29" builtinId="20"/>
-    <cellStyle name="标题 4" xfId="30" builtinId="19"/>
-    <cellStyle name="标题 3" xfId="31" builtinId="18"/>
-    <cellStyle name="标题 2" xfId="32" builtinId="17"/>
-    <cellStyle name="标题 1" xfId="33" builtinId="16"/>
-    <cellStyle name="注释" xfId="34" builtinId="10"/>
-    <cellStyle name="已访问的超链接" xfId="35" builtinId="9"/>
-    <cellStyle name="超链接" xfId="36" builtinId="8"/>
-    <cellStyle name="千位分隔[0]" xfId="37" builtinId="6"/>
-    <cellStyle name="解释性文本" xfId="38" builtinId="53"/>
-    <cellStyle name="货币[0]" xfId="39" builtinId="7"/>
-    <cellStyle name="标题" xfId="40" builtinId="15"/>
-    <cellStyle name="货币" xfId="41" builtinId="4"/>
-    <cellStyle name="好" xfId="42" builtinId="26"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="43" builtinId="50"/>
-    <cellStyle name="千位分隔" xfId="44" builtinId="3"/>
-    <cellStyle name="百分比" xfId="45" builtinId="5"/>
-    <cellStyle name="警告文本" xfId="46" builtinId="11"/>
-    <cellStyle name="检查单元格" xfId="47" builtinId="23"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="48" builtinId="47"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="1" builtinId="47"/>
+    <cellStyle name="检查单元格" xfId="2" builtinId="23"/>
+    <cellStyle name="警告文本" xfId="3" builtinId="11"/>
+    <cellStyle name="千位分隔" xfId="4" builtinId="3"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="5" builtinId="50"/>
+    <cellStyle name="好" xfId="6" builtinId="26"/>
+    <cellStyle name="标题" xfId="7" builtinId="15"/>
+    <cellStyle name="货币[0]" xfId="8" builtinId="7"/>
+    <cellStyle name="解释性文本" xfId="9" builtinId="53"/>
+    <cellStyle name="千位分隔[0]" xfId="10" builtinId="6"/>
+    <cellStyle name="超链接" xfId="11" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="标题 1" xfId="14" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="15" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="16" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="17" builtinId="19"/>
+    <cellStyle name="输入" xfId="18" builtinId="20"/>
+    <cellStyle name="输出" xfId="19" builtinId="21"/>
+    <cellStyle name="计算" xfId="20" builtinId="22"/>
+    <cellStyle name="链接单元格" xfId="21" builtinId="24"/>
+    <cellStyle name="汇总" xfId="22" builtinId="25"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="25" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="26" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="27" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="29" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="30" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="31" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="32" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="33" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="34" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="35" builtinId="40"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="36" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="37" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="38" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="39" builtinId="46"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="40" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="41" builtinId="49"/>
+    <cellStyle name="货币" xfId="42" builtinId="4"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="43" builtinId="51"/>
+    <cellStyle name="强调文字颜色 4" xfId="44" builtinId="41"/>
+    <cellStyle name="强调文字颜色 1" xfId="45" builtinId="29"/>
+    <cellStyle name="百分比" xfId="46" builtinId="5"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="47" builtinId="52"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="48" builtinId="44"/>
   </cellStyles>
 </styleSheet>
 </file>
@@ -5383,9 +5362,9 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="32.375" customWidth="1"/>
-    <col min="2" max="6" width="9" style="15"/>
-    <col min="7" max="7" width="14.875" style="15" customWidth="1"/>
-    <col min="8" max="9" width="9" style="15"/>
+    <col min="2" max="6" width="9" style="16"/>
+    <col min="7" max="7" width="14.875" style="16" customWidth="1"/>
+    <col min="8" max="9" width="9" style="16"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -39463,181 +39442,181 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.6">
-      <c r="A1" s="11" t="s">
-        <v>1403</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>1405</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>1412</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>1416</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>1420</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>1429</v>
+      <c r="A1" s="10" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>1389</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>1390</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>1391</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>1392</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="17.6">
-      <c r="A2" s="10" t="s">
-        <v>1387</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>1406</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>1413</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>1417</v>
+      <c r="A2" s="12" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>1395</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>1396</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>1421</v>
-      </c>
-      <c r="F2" t="s">
-        <v>1430</v>
+        <v>1397</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>1398</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="5" t="s">
-        <v>1404</v>
+        <v>1399</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>1407</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1413</v>
-      </c>
-      <c r="D3" t="s">
-        <v>1418</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>1422</v>
-      </c>
-      <c r="F3" t="s">
-        <v>1431</v>
+        <v>1427</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>1395</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>1401</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>1402</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>1403</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="5" t="s">
-        <v>1389</v>
+        <v>1404</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>1408</v>
-      </c>
-      <c r="C4" t="s">
-        <v>1413</v>
-      </c>
-      <c r="D4" t="s">
-        <v>1418</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>1423</v>
-      </c>
-      <c r="F4" t="s">
-        <v>1432</v>
+        <v>1405</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>1395</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>1401</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>1406</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>1407</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>1392</v>
-      </c>
-      <c r="B5" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>1409</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>1414</v>
-      </c>
-      <c r="D5" t="s">
-        <v>1418</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>1424</v>
-      </c>
-      <c r="F5" t="s">
+        <v>1410</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>1401</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>1411</v>
+      </c>
+      <c r="F5" s="14" t="s">
         <v>1409</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>1394</v>
+        <v>1412</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>1395</v>
-      </c>
-      <c r="C6" t="s">
+        <v>1413</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>1410</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>1401</v>
+      </c>
+      <c r="E6" s="15" t="s">
         <v>1414</v>
       </c>
-      <c r="D6" t="s">
-        <v>1418</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>1425</v>
-      </c>
-      <c r="F6" t="s">
-        <v>1433</v>
+      <c r="F6" s="14" t="s">
+        <v>1415</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="5" t="s">
-        <v>1396</v>
+        <v>1416</v>
       </c>
       <c r="B7" s="5" t="s"/>
       <c r="C7" s="5" t="s">
-        <v>1414</v>
-      </c>
-      <c r="D7" t="s">
+        <v>1410</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>1417</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>1418</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="14" t="s">
         <v>1419</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="B8" s="14" t="s">
+        <v>1420</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>1410</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>1401</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>1421</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="14" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>1423</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>1401</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>1425</v>
+      </c>
+      <c r="F9" s="14" t="s">
         <v>1426</v>
-      </c>
-      <c r="F7" t="s">
-        <v>1419</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
-        <v>1398</v>
-      </c>
-      <c r="B8" t="s">
-        <v>1410</v>
-      </c>
-      <c r="C8" t="s">
-        <v>1414</v>
-      </c>
-      <c r="D8" t="s">
-        <v>1418</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>1427</v>
-      </c>
-      <c r="F8" t="s">
-        <v>1410</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
-        <v>1400</v>
-      </c>
-      <c r="B9" t="s">
-        <v>1411</v>
-      </c>
-      <c r="C9" t="s">
-        <v>1415</v>
-      </c>
-      <c r="D9" t="s">
-        <v>1418</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>1435</v>
-      </c>
-      <c r="F9" t="s">
-        <v>1434</v>
       </c>
     </row>
   </sheetData>

--- a/data/中幼林抚育-网格填表模板.xlsx
+++ b/data/中幼林抚育-网格填表模板.xlsx
@@ -54403,7 +54403,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>拍照;轨迹</t>
+          <t>拍照;视频;轨迹</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -54460,64 +54460,64 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>压缩最长边</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>1440</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>数值</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>1440</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>手机端压缩最长边(px)，仅影响新拍照片</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>1440</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>压缩质量</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>0.8</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>数值</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>0.8</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>JPEG 质量 0.1-1，仅影响新拍照片</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>0.8</t>
         </is>
